--- a/data/trans_orig/IP11D_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP11D_2023-Estudios-trans_orig.xlsx
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>535</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11093</t>
+          <t>9851</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>562</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50911</t>
+          <t>52153</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60976</t>
+          <t>61469</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105131</t>
+          <t>104125</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116134</t>
+          <t>116120</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9771</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7812</t>
+          <t>8735</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14182</t>
+          <t>13424</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>449539</t>
+          <t>450526</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>457808</t>
+          <t>457738</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>507882</t>
+          <t>506959</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>514416</t>
+          <t>514478</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>960822</t>
+          <t>961580</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>970996</t>
+          <t>971123</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4208</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>6722</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1459</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>9391</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>145343</t>
+          <t>145135</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>176515</t>
+          <t>176627</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>182506</t>
+          <t>182702</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>324513</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>331441</t>
+          <t>331437</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10632</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18281</t>
+          <t>17811</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9135</t>
+          <t>8978</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24286</t>
+          <t>24506</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>653467</t>
+          <t>652907</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>661355</t>
+          <t>660938</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>742766</t>
+          <t>743236</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>756143</t>
+          <t>756256</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1400300</t>
+          <t>1400080</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1415451</t>
+          <t>1415608</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP11D_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP11D_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3088</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>17,26%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3616</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9851</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>15,89%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>420</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>53644</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>46940</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>56298</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,56%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>82,74%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>46758</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>58388</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>52153</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>61469</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>94,17%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>84,11%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>149</t>
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>113066</t>
+          <t>100402</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>104125</t>
+          <t>94250</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116120</t>
+          <t>103070</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3126</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1134</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7263</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4186</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1572</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8784</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3455</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,22 +1138,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>7311</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13424</t>
+          <t>13079</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>471593</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>467456</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>473585</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,47%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>635</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>455124</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>450526</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>457738</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>512239</t>
+          <t>427068</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>506959</t>
+          <t>422360</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>514478</t>
+          <t>429565</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>967364</t>
+          <t>898661</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>961580</t>
+          <t>892893</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>971123</t>
+          <t>902316</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>474719</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>474719</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>474719</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>641</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>459310</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>459310</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>459310</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>515694</t>
+          <t>431253</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>515694</t>
+          <t>431253</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>515694</t>
+          <t>431253</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>975004</t>
+          <t>905972</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>975004</t>
+          <t>905972</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>975004</t>
+          <t>905972</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6352</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1208</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1269</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4416</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4448</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2615</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6722</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9391</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -1519,74 +1519,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>165998</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>162067</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>167773</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,56%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,23%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>148343</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>145135</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,05%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>148707</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>145528</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>149976</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,03%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>180734</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>176627</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>182702</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,57%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,33%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>463</t>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>329076</t>
+          <t>314705</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>323509</t>
+          <t>310663</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>331437</t>
+          <t>317150</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,107 +1749,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8635</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16081</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5394</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2601</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10632</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17811</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>14089</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>8359</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>22675</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>15080</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>8978</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>24506</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>965</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>691235</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>683789</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>695476</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,7%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>932</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>658145</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>652907</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>660938</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>965</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>751360</t>
+          <t>622533</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>743236</t>
+          <t>617239</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>756256</t>
+          <t>625667</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1409506</t>
+          <t>1313768</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1400080</t>
+          <t>1305182</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1415608</t>
+          <t>1319498</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>699870</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>699870</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>699870</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>940</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>663539</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>663539</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>663539</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761047</t>
+          <t>627987</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761047</t>
+          <t>627987</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761047</t>
+          <t>627987</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1424586</t>
+          <t>1327857</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1424586</t>
+          <t>1327857</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1424586</t>
+          <t>1327857</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
